--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G60" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G68" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,17 +8086,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,17 +9071,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G68" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,17 +8086,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,17 +8480,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.48</v>
+        <v>1.32</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.86</v>
+        <v>6.09</v>
       </c>
       <c r="R41" t="n">
-        <v>2.13</v>
+        <v>10.6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,17 +8283,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,17 +8480,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,17 +8283,17 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,17 +8874,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,17 +8086,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,17 +8874,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G68" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,17 +7889,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.48</v>
+        <v>1.32</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.86</v>
+        <v>6.09</v>
       </c>
       <c r="R38" t="n">
-        <v>2.13</v>
+        <v>10.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8086,17 +8086,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G68" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,17 +7889,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.32</v>
+        <v>2.92</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.09</v>
+        <v>3.55</v>
       </c>
       <c r="R38" t="n">
-        <v>10.6</v>
+        <v>2.2</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.48</v>
+        <v>1.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="R41" t="n">
-        <v>2.13</v>
+        <v>4.87</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,17 +8677,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>3.13</v>
+        <v>2.75</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>2.75</v>
+        <v>3.77</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.63</v>
+        <v>3.48</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="R41" t="n">
-        <v>4.87</v>
+        <v>2.13</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,17 +8677,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,17 +9071,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.48</v>
+        <v>1.32</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.86</v>
+        <v>6.09</v>
       </c>
       <c r="R44" t="n">
-        <v>2.13</v>
+        <v>10.6</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G67" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.99</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
       <c r="R21" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>2.99</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3.61</v>
       </c>
       <c r="R29" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,17 +7889,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.63</v>
+        <v>3.48</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="R40" t="n">
-        <v>4.87</v>
+        <v>2.13</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.48</v>
+        <v>2.92</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.86</v>
+        <v>3.55</v>
       </c>
       <c r="R41" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,17 +9071,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9613,12 +9613,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46155.79166666666</v>
+        <v>46155.77083333334</v>
       </c>
     </row>
     <row r="48">
@@ -9810,12 +9810,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46155.83333333334</v>
+        <v>46155.79166666666</v>
       </c>
     </row>
     <row r="49">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46155.85416666666</v>
+        <v>46155.83333333334</v>
       </c>
     </row>
     <row r="51">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11386,27 +11386,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46155.875</v>
+        <v>46155.85416666666</v>
       </c>
     </row>
     <row r="57">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46155.89583333334</v>
+        <v>46155.875</v>
       </c>
     </row>
     <row r="62">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13159,12 +13159,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46155.91666666666</v>
+        <v>46155.89583333334</v>
       </c>
     </row>
     <row r="66">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G68" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.17</v>
+        <v>2.99</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="R23" t="n">
-        <v>3.08</v>
+        <v>2.48</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.99</v>
+        <v>2.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.61</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>2.48</v>
+        <v>3.13</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.42</v>
+        <v>2.17</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>6.28</v>
+        <v>3.08</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,17 +7889,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.32</v>
+        <v>3.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.09</v>
+        <v>3.86</v>
       </c>
       <c r="R38" t="n">
-        <v>10.6</v>
+        <v>2.13</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,17 +8677,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.9</v>
+        <v>6.09</v>
       </c>
       <c r="R42" t="n">
-        <v>4.87</v>
+        <v>10.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G68" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.41</v>
+        <v>1.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R17" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>7.22</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>2.75</v>
+        <v>3.08</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.17</v>
+        <v>2.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.92</v>
+        <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="R43" t="n">
-        <v>2.2</v>
+        <v>4.87</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G65" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.41</v>
+        <v>1.44</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>7.22</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>3.13</v>
+        <v>2.75</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>3.08</v>
+        <v>3.77</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.92</v>
+        <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="R44" t="n">
-        <v>2.2</v>
+        <v>4.87</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G65" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="Q26" t="n">
         <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.86</v>
+        <v>2.13</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>3.77</v>
+        <v>3.13</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,17 +8677,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.09</v>
+        <v>3.9</v>
       </c>
       <c r="R42" t="n">
-        <v>10.6</v>
+        <v>4.87</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G68" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.31</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>4.57</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>7.22</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.41</v>
+        <v>1.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R17" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>2.75</v>
+        <v>3.77</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.86</v>
+        <v>2.13</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>3.77</v>
+        <v>3.13</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G68" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>3.31</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>4.57</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.44</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>7.22</v>
+        <v>2.87</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>3.08</v>
+        <v>3.77</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.48</v>
+        <v>1.32</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.86</v>
+        <v>6.09</v>
       </c>
       <c r="R40" t="n">
-        <v>2.13</v>
+        <v>10.6</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.32</v>
+        <v>3.48</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.09</v>
+        <v>3.86</v>
       </c>
       <c r="R43" t="n">
-        <v>10.6</v>
+        <v>2.13</v>
       </c>
       <c r="S43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G68" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.31</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>4.57</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R19" t="n">
-        <v>3.08</v>
+        <v>3.77</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.42</v>
+        <v>2.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>6.28</v>
+        <v>3.13</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.09</v>
+        <v>3.9</v>
       </c>
       <c r="R40" t="n">
-        <v>10.6</v>
+        <v>4.87</v>
       </c>
       <c r="S40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.48</v>
+        <v>1.32</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.86</v>
+        <v>6.09</v>
       </c>
       <c r="R43" t="n">
-        <v>2.13</v>
+        <v>10.6</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.92</v>
+        <v>3.48</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.55</v>
+        <v>3.86</v>
       </c>
       <c r="R44" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G68" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.86</v>
+        <v>2.99</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="R19" t="n">
-        <v>3.77</v>
+        <v>2.48</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>6.28</v>
+        <v>2.75</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.99</v>
+        <v>1.42</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.61</v>
+        <v>4.6</v>
       </c>
       <c r="R30" t="n">
-        <v>2.48</v>
+        <v>6.28</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.48</v>
+        <v>1.32</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.86</v>
+        <v>6.09</v>
       </c>
       <c r="R44" t="n">
-        <v>2.13</v>
+        <v>10.6</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G68" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI68"/>
+  <dimension ref="A1:BI70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.31</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="R7" t="n">
-        <v>2.16</v>
+        <v>4.57</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>7.22</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.99</v>
+        <v>2.17</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.61</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>2.48</v>
+        <v>3.08</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>1.86</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>2.75</v>
+        <v>3.77</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>6.28</v>
+        <v>2.75</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.92</v>
+        <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="R39" t="n">
-        <v>2.2</v>
+        <v>4.87</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9613,27 +9613,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46155.77083333334</v>
+        <v>46155.79166666666</v>
       </c>
     </row>
     <row r="48">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46155.85416666666</v>
+        <v>46155.83333333334</v>
       </c>
     </row>
     <row r="52">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46155.875</v>
+        <v>46155.85416666666</v>
       </c>
     </row>
     <row r="58">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12568,27 +12568,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46155.89583333334</v>
+        <v>46155.875</v>
       </c>
     </row>
     <row r="63">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46155.9375</v>
+        <v>46155.89583333334</v>
       </c>
     </row>
     <row r="67">
@@ -13553,27 +13553,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46155.9375</v>
+        <v>46155.91666666666</v>
       </c>
     </row>
     <row r="68">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13938,6 +13938,400 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3" t="n">
+        <v>46155.9375</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N69" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI69" s="3" t="n">
+        <v>46155.9375</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>0</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI70" s="3" t="n">
         <v>46155.9375</v>
       </c>
     </row>

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>7.22</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.99</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.61</v>
+        <v>3.3</v>
       </c>
       <c r="R21" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="Q28" t="n">
         <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.86</v>
+        <v>2.99</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="R29" t="n">
-        <v>3.77</v>
+        <v>2.48</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.32</v>
+        <v>3.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.09</v>
+        <v>3.86</v>
       </c>
       <c r="R38" t="n">
-        <v>10.6</v>
+        <v>2.13</v>
       </c>
       <c r="S38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="R39" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="S39" t="n">
         <v>1.63</v>
       </c>
-      <c r="Q39" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R39" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.48</v>
+        <v>2.92</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.86</v>
+        <v>3.55</v>
       </c>
       <c r="R42" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G70" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.31</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2.16</v>
+        <v>4.57</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.44</v>
+        <v>2.41</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>7.22</v>
+        <v>2.87</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.13</v>
+        <v>2.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="R20" t="n">
-        <v>3.13</v>
+        <v>2.48</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>3.08</v>
+        <v>3.77</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.48</v>
+        <v>1.32</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.86</v>
+        <v>6.09</v>
       </c>
       <c r="R38" t="n">
-        <v>2.13</v>
+        <v>10.6</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,133 +8090,133 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.32</v>
+        <v>3.48</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.09</v>
+        <v>3.86</v>
       </c>
       <c r="R39" t="n">
-        <v>10.6</v>
+        <v>2.13</v>
       </c>
       <c r="S39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV39" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.63</v>
+        <v>2.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="R44" t="n">
-        <v>4.87</v>
+        <v>2.2</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G70" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>2.34</v>
+        <v>4.57</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.41</v>
+        <v>1.44</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>7.22</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.86</v>
+        <v>1.42</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="R28" t="n">
-        <v>3.77</v>
+        <v>6.28</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,133 +7893,133 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.32</v>
+        <v>2.92</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.09</v>
+        <v>3.55</v>
       </c>
       <c r="R38" t="n">
-        <v>10.6</v>
+        <v>2.2</v>
       </c>
       <c r="S38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.63</v>
+        <v>3.48</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="R41" t="n">
-        <v>4.87</v>
+        <v>2.13</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G70" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.44</v>
+        <v>2.41</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="R16" t="n">
-        <v>7.22</v>
+        <v>2.87</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.6</v>
+        <v>3.34</v>
       </c>
       <c r="R28" t="n">
-        <v>6.28</v>
+        <v>4.53</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>2.99</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>3.61</v>
       </c>
       <c r="R31" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>3.08</v>
+        <v>3.77</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.92</v>
+        <v>1.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="R38" t="n">
-        <v>2.2</v>
+        <v>4.87</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.48</v>
+        <v>1.32</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.86</v>
+        <v>6.09</v>
       </c>
       <c r="R41" t="n">
-        <v>2.13</v>
+        <v>10.6</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G69" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>3.31</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>4.57</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.44</v>
+        <v>2.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="R17" t="n">
-        <v>7.22</v>
+        <v>2.87</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.13</v>
+        <v>1.42</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R19" t="n">
-        <v>3.13</v>
+        <v>6.28</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.6</v>
+        <v>3.34</v>
       </c>
       <c r="R21" t="n">
-        <v>6.28</v>
+        <v>4.53</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.86</v>
+        <v>2.17</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>3.77</v>
+        <v>3.08</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.32</v>
+        <v>2.92</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.09</v>
+        <v>3.55</v>
       </c>
       <c r="R41" t="n">
-        <v>10.6</v>
+        <v>2.2</v>
       </c>
       <c r="S41" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G70" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="R24" t="n">
-        <v>2.75</v>
+        <v>4.53</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.99</v>
+        <v>1.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.61</v>
+        <v>4.6</v>
       </c>
       <c r="R26" t="n">
-        <v>2.48</v>
+        <v>6.28</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>3.08</v>
+        <v>3.77</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.32</v>
+        <v>3.48</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.09</v>
+        <v>3.86</v>
       </c>
       <c r="R42" t="n">
-        <v>10.6</v>
+        <v>2.13</v>
       </c>
       <c r="S42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.48</v>
+        <v>1.32</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.86</v>
+        <v>6.09</v>
       </c>
       <c r="R44" t="n">
-        <v>2.13</v>
+        <v>10.6</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G66" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.31</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>4.57</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.41</v>
+        <v>1.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R17" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.44</v>
+        <v>2.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>7.22</v>
+        <v>2.87</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>3.08</v>
+        <v>3.77</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.86</v>
+        <v>2.17</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>3.77</v>
+        <v>3.08</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.48</v>
+        <v>1.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="R42" t="n">
-        <v>2.13</v>
+        <v>4.87</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.32</v>
+        <v>2.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.09</v>
+        <v>3.55</v>
       </c>
       <c r="R44" t="n">
-        <v>10.6</v>
+        <v>2.2</v>
       </c>
       <c r="S44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G69" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI70"/>
+  <dimension ref="A1:BI73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.31</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="R8" t="n">
-        <v>2.16</v>
+        <v>4.57</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3112,27 +3112,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46155.52083333334</v>
+        <v>46155.5</v>
       </c>
     </row>
     <row r="15">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46155.54166666666</v>
+        <v>46155.5</v>
       </c>
     </row>
     <row r="16">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46155.5625</v>
+        <v>46155.5</v>
       </c>
     </row>
     <row r="17">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>7.22</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46155.5625</v>
+        <v>46155.52083333334</v>
       </c>
     </row>
     <row r="18">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.41</v>
+        <v>3.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>2.87</v>
+        <v>2.24</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46155.5625</v>
+        <v>46155.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46155.58333333334</v>
+        <v>46155.5625</v>
       </c>
     </row>
     <row r="20">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46155.58333333334</v>
+        <v>46155.5625</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>3.07</v>
+        <v>7.22</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46155.58333333334</v>
+        <v>46155.5625</v>
       </c>
     </row>
     <row r="22">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.73</v>
+        <v>2.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.34</v>
+        <v>3.61</v>
       </c>
       <c r="R27" t="n">
-        <v>4.53</v>
+        <v>2.48</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.86</v>
+        <v>2.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>3.77</v>
+        <v>3.13</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>3.13</v>
+        <v>2.75</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>3.08</v>
+        <v>3.77</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46155.59375</v>
+        <v>46155.58333333334</v>
       </c>
     </row>
     <row r="34">
@@ -7052,27 +7052,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.79</v>
+        <v>2.17</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>3.79</v>
+        <v>3.08</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46155.60416666666</v>
+        <v>46155.58333333334</v>
       </c>
     </row>
     <row r="35">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46155.625</v>
+        <v>46155.58333333334</v>
       </c>
     </row>
     <row r="36">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46155.625</v>
+        <v>46155.59375</v>
       </c>
     </row>
     <row r="37">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46155.64583333334</v>
+        <v>46155.60416666666</v>
       </c>
     </row>
     <row r="38">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46155.66666666666</v>
+        <v>46155.625</v>
       </c>
     </row>
     <row r="39">
@@ -8037,27 +8037,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46155.66666666666</v>
+        <v>46155.625</v>
       </c>
     </row>
     <row r="40">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46155.66666666666</v>
+        <v>46155.64583333334</v>
       </c>
     </row>
     <row r="41">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="R42" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="S42" t="n">
         <v>1.63</v>
       </c>
-      <c r="Q42" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R42" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9219,27 +9219,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46155.6875</v>
+        <v>46155.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46155.6875</v>
+        <v>46155.66666666666</v>
       </c>
     </row>
     <row r="47">
@@ -9613,27 +9613,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46155.79166666666</v>
+        <v>46155.66666666666</v>
       </c>
     </row>
     <row r="48">
@@ -9810,12 +9810,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46155.79166666666</v>
+        <v>46155.6875</v>
       </c>
     </row>
     <row r="49">
@@ -10007,27 +10007,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46155.83333333334</v>
+        <v>46155.6875</v>
       </c>
     </row>
     <row r="50">
@@ -10204,27 +10204,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46155.83333333334</v>
+        <v>46155.79166666666</v>
       </c>
     </row>
     <row r="51">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46155.83333333334</v>
+        <v>46155.79166666666</v>
       </c>
     </row>
     <row r="52">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46155.85416666666</v>
+        <v>46155.83333333334</v>
       </c>
     </row>
     <row r="53">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46155.85416666666</v>
+        <v>46155.83333333334</v>
       </c>
     </row>
     <row r="54">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46155.85416666666</v>
+        <v>46155.84375</v>
       </c>
     </row>
     <row r="55">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11780,12 +11780,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11968,7 +11968,7 @@
         <v>0</v>
       </c>
       <c r="BI58" s="3" t="n">
-        <v>46155.875</v>
+        <v>46155.85416666666</v>
       </c>
     </row>
     <row r="59">
@@ -11977,27 +11977,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12165,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
-        <v>46155.875</v>
+        <v>46155.85416666666</v>
       </c>
     </row>
     <row r="60">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46155.875</v>
+        <v>46155.85416666666</v>
       </c>
     </row>
     <row r="61">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>46155.89583333334</v>
+        <v>46155.875</v>
       </c>
     </row>
     <row r="64">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46155.89583333334</v>
+        <v>46155.875</v>
       </c>
     </row>
     <row r="65">
@@ -13159,12 +13159,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46155.89583333334</v>
+        <v>46155.875</v>
       </c>
     </row>
     <row r="66">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13553,27 +13553,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46155.91666666666</v>
+        <v>46155.89583333334</v>
       </c>
     </row>
     <row r="68">
@@ -13750,7 +13750,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13938,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>46155.9375</v>
+        <v>46155.89583333334</v>
       </c>
     </row>
     <row r="69">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>46155.9375</v>
+        <v>46155.89583333334</v>
       </c>
     </row>
     <row r="70">
@@ -14144,27 +14144,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14332,6 +14332,597 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3" t="n">
+        <v>46155.91666666666</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>SJ Earthquakes</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI71" s="3" t="n">
+        <v>46155.9375</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Houston Dynamo</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI72" s="3" t="n">
+        <v>46155.9375</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI73" s="3" t="n">
         <v>46155.9375</v>
       </c>
     </row>

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="R6" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.4</v>
+        <v>3.31</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.65</v>
+        <v>3.25</v>
       </c>
       <c r="R7" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>7.22</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.17</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>2.24</v>
+        <v>2.75</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.99</v>
+        <v>1.86</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>2.48</v>
+        <v>3.77</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.92</v>
+        <v>1.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="R46" t="n">
-        <v>2.2</v>
+        <v>4.87</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="R47" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="S47" t="n">
         <v>1.63</v>
       </c>
-      <c r="Q47" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R47" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G73" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.44</v>
+        <v>2.41</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>7.22</v>
+        <v>2.87</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.41</v>
+        <v>1.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R20" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>3.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>2.75</v>
+        <v>2.24</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.42</v>
+        <v>2.16</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>6.28</v>
+        <v>3.07</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.13</v>
+        <v>1.42</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R24" t="n">
-        <v>3.13</v>
+        <v>6.28</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>4.53</v>
+        <v>2.75</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.17</v>
+        <v>1.86</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>2.24</v>
+        <v>3.77</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7944,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.92</v>
+        <v>1.32</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.55</v>
+        <v>6.09</v>
       </c>
       <c r="R44" t="n">
-        <v>2.2</v>
+        <v>10.6</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU47" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G73" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1401,121 +1401,121 @@
         <v>3.08</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD5" t="n">
         <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG9" t="n">
         <v>3.9</v>
       </c>
-      <c r="R9" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>4.99</v>
+        <v>3.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.41</v>
+        <v>1.44</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R19" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.44</v>
+        <v>2.41</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>7.22</v>
+        <v>2.87</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.42</v>
+        <v>3.17</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>6.28</v>
+        <v>2.24</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>2.99</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>3.61</v>
       </c>
       <c r="R26" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.99</v>
+        <v>1.73</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.61</v>
+        <v>3.34</v>
       </c>
       <c r="R28" t="n">
-        <v>2.48</v>
+        <v>4.53</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.13</v>
+        <v>1.86</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>3.13</v>
+        <v>3.77</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7944,10 +7944,10 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.48</v>
+        <v>2.92</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.86</v>
+        <v>3.55</v>
       </c>
       <c r="R41" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.92</v>
+        <v>3.48</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.55</v>
+        <v>3.86</v>
       </c>
       <c r="R42" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>6.09</v>
+      </c>
+      <c r="R46" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="S46" t="n">
         <v>1.63</v>
       </c>
-      <c r="Q46" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R46" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G73" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>2.22</v>
+        <v>4.28</v>
       </c>
       <c r="T6" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="U6" t="n">
-        <v>5.04</v>
+        <v>2.87</v>
       </c>
       <c r="V6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX6" t="n">
         <v>1.32</v>
       </c>
-      <c r="W6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.25</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>3.84</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="S7" t="n">
-        <v>4.93</v>
+        <v>2.22</v>
       </c>
       <c r="T7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.7</v>
       </c>
-      <c r="U7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y7" t="n">
+      <c r="AF7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AN7" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF7" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.03</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK8" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="AL8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BC8" t="n">
         <v>3</v>
       </c>
-      <c r="S8" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="BD8" t="n">
         <v>2.59</v>
       </c>
-      <c r="AF8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ8" t="n">
+      <c r="BE8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF8" t="n">
         <v>1.03</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.05</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>4.28</v>
+        <v>3.19</v>
       </c>
       <c r="T9" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="U9" t="n">
-        <v>2.87</v>
+        <v>3.95</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="W9" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="X9" t="n">
-        <v>3.15</v>
+        <v>3.68</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.85</v>
+        <v>2.29</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.19</v>
+        <v>2.59</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.9</v>
+        <v>5.64</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AI9" t="n">
-        <v>8.1</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV9" t="n">
         <v>1.87</v>
       </c>
-      <c r="AL9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AW9" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AX9" t="n">
         <v>1.32</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>2.43</v>
+        <v>1.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.17</v>
+        <v>3.49</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="R18" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4159,124 +4159,124 @@
         <v>7.22</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4356,124 +4356,124 @@
         <v>2.87</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,28 +4938,28 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.13</v>
+        <v>3.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>3.13</v>
+        <v>2.24</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -4977,40 +4977,40 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5055,13 +5055,13 @@
         <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.17</v>
+        <v>1.86</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>2.24</v>
+        <v>3.77</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>3.07</v>
+        <v>3.18</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,22 +5529,22 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.99</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>2.48</v>
+        <v>3.07</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5553,10 +5553,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -5568,40 +5568,40 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5646,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.65</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>2.91</v>
+        <v>2.34</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.73</v>
+        <v>2.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.34</v>
+        <v>2.65</v>
       </c>
       <c r="R28" t="n">
-        <v>4.53</v>
+        <v>2.91</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7508,40 +7508,40 @@
         <v>3.63</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE36" t="n">
         <v>2.1</v>
@@ -7550,82 +7550,82 @@
         <v>1.65</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7696,79 +7696,79 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="Q37" t="n">
         <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>3.79</v>
+        <v>3.9</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
@@ -7810,19 +7810,19 @@
         <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8099,46 +8099,46 @@
         <v>24</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG39" t="n">
         <v>1.85</v>
@@ -8147,22 +8147,22 @@
         <v>1.89</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8177,10 +8177,10 @@
         <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AU39" t="n">
         <v>0</v>
@@ -8192,31 +8192,31 @@
         <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8287,133 +8287,133 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="R40" t="n">
         <v>3.35</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE40" t="n">
         <v>1.75</v>
       </c>
       <c r="AF40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC40" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>0</v>
-      </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8493,124 +8493,124 @@
         <v>2.2</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB41" t="n">
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q42" t="n">
         <v>3.48</v>
       </c>
-      <c r="Q42" t="n">
-        <v>3.86</v>
-      </c>
       <c r="R42" t="n">
-        <v>2.13</v>
+        <v>3.63</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.98</v>
+        <v>3.24</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.48</v>
+        <v>3.84</v>
       </c>
       <c r="R45" t="n">
-        <v>3.64</v>
+        <v>2.06</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.91</v>
+        <v>1.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.32</v>
+        <v>1.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>6.09</v>
+        <v>3.9</v>
       </c>
       <c r="R46" t="n">
-        <v>10.6</v>
+        <v>4.87</v>
       </c>
       <c r="S46" t="n">
-        <v>1.63</v>
+        <v>2.14</v>
       </c>
       <c r="T46" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U46" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W46" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X46" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW46" t="n">
         <v>2.7</v>
       </c>
-      <c r="U46" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W46" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AX46" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="BD46" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="BE46" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G73" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>4.28</v>
+        <v>4.93</v>
       </c>
       <c r="T6" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="W6" t="n">
-        <v>2.63</v>
+        <v>2.02</v>
       </c>
       <c r="X6" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.1</v>
+        <v>13</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.02</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1670,52 +1670,52 @@
         <v>1.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.84</v>
+        <v>2.8</v>
       </c>
       <c r="R7" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>2.22</v>
+        <v>3.19</v>
       </c>
       <c r="T7" t="n">
-        <v>2.22</v>
+        <v>1.77</v>
       </c>
       <c r="U7" t="n">
-        <v>5.04</v>
+        <v>3.95</v>
       </c>
       <c r="V7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX7" t="n">
         <v>1.32</v>
       </c>
-      <c r="W7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>1.7</v>
       </c>
-      <c r="AF7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="BA7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE7" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BF7" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3.25</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.75</v>
-      </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>4.93</v>
+        <v>4.28</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="U8" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="X8" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="Z8" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.88</v>
+        <v>2.19</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AI8" t="n">
-        <v>13</v>
+        <v>8.1</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.02</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,52 +2064,52 @@
         <v>1.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AW8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA8" t="n">
         <v>1.64</v>
       </c>
-      <c r="AX8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA8" t="n">
+      <c r="BB8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE8" t="n">
         <v>1.53</v>
       </c>
-      <c r="BB8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BF8" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.8</v>
+        <v>3.84</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="S9" t="n">
-        <v>3.19</v>
+        <v>2.22</v>
       </c>
       <c r="T9" t="n">
-        <v>1.77</v>
+        <v>2.22</v>
       </c>
       <c r="U9" t="n">
-        <v>3.95</v>
+        <v>5.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="X9" t="n">
-        <v>3.68</v>
+        <v>2.47</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.55</v>
+        <v>1.19</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.29</v>
+        <v>3.98</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.59</v>
+        <v>1.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.64</v>
+        <v>2.57</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
-        <v>12</v>
+        <v>4.7</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.59</v>
+        <v>2.08</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.5</v>
+        <v>2.07</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.75</v>
+        <v>1.89</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>2.27</v>
+        <v>3.13</v>
       </c>
       <c r="S22" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,28 +4938,28 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.17</v>
+        <v>2.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="S23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -4977,40 +4977,40 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5055,13 +5055,13 @@
         <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
         <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>1.42</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="R25" t="n">
-        <v>3.18</v>
+        <v>6.28</v>
       </c>
       <c r="S25" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.65</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,22 +5529,22 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>3.07</v>
+        <v>3.77</v>
       </c>
       <c r="S26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5553,10 +5553,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -5568,40 +5568,40 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5646,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>2.34</v>
+        <v>3.07</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="T27" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK27" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z27" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AL27" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.57</v>
+        <v>3.17</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>2.91</v>
+        <v>2.24</v>
       </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL28" t="n">
         <v>1.85</v>
       </c>
-      <c r="U28" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AM28" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q31" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="R31" t="n">
-        <v>6.28</v>
+        <v>2.75</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>5.06</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="Q34" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BD34" t="n">
         <v>3.4</v>
       </c>
-      <c r="R34" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.73</v>
+        <v>2.57</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.34</v>
+        <v>2.65</v>
       </c>
       <c r="R35" t="n">
-        <v>4.53</v>
+        <v>2.91</v>
       </c>
       <c r="S35" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="T35" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="U35" t="n">
-        <v>5.06</v>
+        <v>3.7</v>
       </c>
       <c r="V35" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="W35" t="n">
-        <v>2.48</v>
+        <v>2.01</v>
       </c>
       <c r="X35" t="n">
-        <v>3.02</v>
+        <v>3.9</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AC35" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AF35" t="n">
         <v>1.34</v>
       </c>
-      <c r="AD35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AG35" t="n">
-        <v>3.58</v>
+        <v>5.4</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AI35" t="n">
-        <v>6.9</v>
+        <v>13.5</v>
       </c>
       <c r="AJ35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BF35" t="n">
         <v>1.04</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>1.11</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.48</v>
+        <v>1.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="R38" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -7980,10 +7980,10 @@
         <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AU38" t="n">
         <v>0</v>
@@ -7995,31 +7995,31 @@
         <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="Q39" t="n">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="R39" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="S39" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8177,10 +8177,10 @@
         <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
         <v>0</v>
@@ -8192,31 +8192,31 @@
         <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.92</v>
+        <v>1.43</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.55</v>
+        <v>4.54</v>
       </c>
       <c r="R41" t="n">
-        <v>2.2</v>
+        <v>6.97</v>
       </c>
       <c r="S41" t="n">
-        <v>3.25</v>
+        <v>2.14</v>
       </c>
       <c r="T41" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="U41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW41" t="n">
         <v>2.7</v>
       </c>
-      <c r="V41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W41" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK41" t="n">
+      <c r="AX41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AZ41" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL41" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS41" t="n">
+      <c r="BA41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE41" t="n">
         <v>1.81</v>
       </c>
-      <c r="AT41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>2</v>
-      </c>
       <c r="BF41" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.98</v>
+        <v>3.24</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.48</v>
+        <v>3.84</v>
       </c>
       <c r="R42" t="n">
-        <v>3.63</v>
+        <v>2.06</v>
       </c>
       <c r="S42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T42" t="n">
         <v>2.5</v>
       </c>
-      <c r="T42" t="n">
-        <v>2.15</v>
-      </c>
       <c r="U42" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="V42" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="W42" t="n">
-        <v>2.81</v>
+        <v>3.7</v>
       </c>
       <c r="X42" t="n">
-        <v>2.81</v>
+        <v>2.2</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="Z42" t="n">
-        <v>6.85</v>
+        <v>4.95</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC42" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN42" t="n">
         <v>1.3</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT42" t="n">
         <v>3.3</v>
       </c>
-      <c r="AE42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM42" t="n">
+      <c r="AU42" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BF42" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>1.17</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.32</v>
+        <v>1.98</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.09</v>
+        <v>3.48</v>
       </c>
       <c r="R44" t="n">
-        <v>10.6</v>
+        <v>3.63</v>
       </c>
       <c r="S44" t="n">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="T44" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="U44" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="V44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W44" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X44" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BB44" t="n">
         <v>1.25</v>
       </c>
-      <c r="W44" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y44" t="n">
+      <c r="BC44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE44" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
+      <c r="BF44" t="n">
         <v>1.17</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>2</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.24</v>
+        <v>2.92</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="R45" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S45" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T45" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U45" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="V45" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W45" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="X45" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.95</v>
+        <v>5.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AD45" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AI45" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK45" t="n">
         <v>1.44</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="AM45" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF45" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE45" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BF45" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>6.09</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G73" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3.25</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2.75</v>
-      </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>4.93</v>
+        <v>4.28</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="U6" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="W6" t="n">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="X6" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.14</v>
+        <v>2.85</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.88</v>
+        <v>2.19</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="AG6" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AI6" t="n">
-        <v>13</v>
+        <v>8.1</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.02</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1670,52 +1670,52 @@
         <v>1.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AW6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA6" t="n">
         <v>1.64</v>
       </c>
-      <c r="AX6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA6" t="n">
+      <c r="BB6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.53</v>
       </c>
-      <c r="BB6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BF6" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W8" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="X8" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF8" t="n">
         <v>2.1</v>
       </c>
-      <c r="S8" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AF8" t="n">
+      <c r="AG8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.65</v>
       </c>
-      <c r="AG8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AL8" t="n">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.29</v>
+        <v>2.07</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.33</v>
+        <v>1.89</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.61</v>
+        <v>3.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.84</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>2.22</v>
+        <v>4.93</v>
       </c>
       <c r="T9" t="n">
-        <v>2.22</v>
+        <v>1.7</v>
       </c>
       <c r="U9" t="n">
-        <v>5.04</v>
+        <v>3.2</v>
       </c>
       <c r="V9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.32</v>
       </c>
-      <c r="W9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR9" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.89</v>
+        <v>3</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.4</v>
+        <v>2.59</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.22</v>
+        <v>1.03</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>7.22</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.17</v>
+        <v>1.42</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="R23" t="n">
-        <v>3.08</v>
+        <v>6.28</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.42</v>
+        <v>2.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.6</v>
+        <v>3.18</v>
       </c>
       <c r="R25" t="n">
-        <v>6.28</v>
+        <v>2.27</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,22 +5529,22 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>3.77</v>
+        <v>3.07</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5553,10 +5553,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -5568,40 +5568,40 @@
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5646,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>3.07</v>
+        <v>3.18</v>
       </c>
       <c r="S27" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="T27" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X27" t="n">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BF27" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>1.86</v>
       </c>
       <c r="Q30" t="n">
         <v>3.6</v>
       </c>
       <c r="R30" t="n">
-        <v>2.34</v>
+        <v>3.77</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>2.75</v>
+        <v>3.13</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="R32" t="n">
-        <v>4.53</v>
+        <v>2.34</v>
       </c>
       <c r="S32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W32" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS32" t="n">
         <v>2.5</v>
       </c>
-      <c r="T32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U32" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="X32" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN32" t="n">
+      <c r="AT32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BE32" t="n">
         <v>1.78</v>
       </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BF32" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>2.57</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="R33" t="n">
-        <v>3.18</v>
+        <v>2.91</v>
       </c>
       <c r="S33" t="n">
-        <v>2.61</v>
+        <v>3.4</v>
       </c>
       <c r="T33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR33" t="n">
         <v>2.3</v>
       </c>
-      <c r="U33" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG33" t="n">
+      <c r="AS33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC33" t="n">
         <v>3</v>
       </c>
-      <c r="AH33" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY33" t="n">
+      <c r="BD33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BE33" t="n">
         <v>1.35</v>
       </c>
-      <c r="AZ33" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BF33" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="R34" t="n">
-        <v>2.27</v>
+        <v>4.53</v>
       </c>
       <c r="S34" t="n">
-        <v>3.22</v>
+        <v>2.5</v>
       </c>
       <c r="T34" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>2.75</v>
+        <v>5.06</v>
       </c>
       <c r="V34" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>2.76</v>
+        <v>2.48</v>
       </c>
       <c r="X34" t="n">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="Z34" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AA34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AJ34" t="n">
         <v>1.04</v>
       </c>
-      <c r="AB34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH34" t="n">
+      <c r="AK34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BB34" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.28</v>
-      </c>
       <c r="BC34" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="R35" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="S35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.54</v>
+        <v>6.09</v>
       </c>
       <c r="R41" t="n">
-        <v>6.97</v>
+        <v>10.6</v>
       </c>
       <c r="S41" t="n">
-        <v>2.14</v>
+        <v>1.63</v>
       </c>
       <c r="T41" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="U41" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="V41" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W41" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="X41" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="Z41" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AD41" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AI41" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BA41" t="n">
         <v>5.5</v>
       </c>
-      <c r="AJ41" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BB41" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.98</v>
+        <v>1.43</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.48</v>
+        <v>4.54</v>
       </c>
       <c r="R44" t="n">
-        <v>3.63</v>
+        <v>6.97</v>
       </c>
       <c r="S44" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="T44" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="U44" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="V44" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W44" t="n">
-        <v>2.81</v>
+        <v>3.15</v>
       </c>
       <c r="X44" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="Z44" t="n">
-        <v>6.85</v>
+        <v>6</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AE44" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC44" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF44" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BD44" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT47" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU47" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11490,10 +11490,10 @@
         <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G73" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S6" t="n">
-        <v>4.28</v>
+        <v>4.93</v>
       </c>
       <c r="T6" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="W6" t="n">
-        <v>2.63</v>
+        <v>2.02</v>
       </c>
       <c r="X6" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.1</v>
+        <v>13</v>
       </c>
       <c r="AJ6" t="n">
         <v>1.02</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1670,52 +1670,52 @@
         <v>1.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS7" t="n">
         <v>2.8</v>
       </c>
-      <c r="R7" t="n">
-        <v>3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="AT7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW7" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.53</v>
       </c>
       <c r="AX7" t="n">
         <v>1.32</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.7</v>
+        <v>2.43</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BC9" t="n">
         <v>2.75</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
+      <c r="BD9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.4</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3562,10 +3562,10 @@
         <v>1.19</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.75</v>
+        <v>5.5</v>
       </c>
       <c r="R16" t="n">
-        <v>7.8</v>
+        <v>11.8</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>7.22</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.41</v>
+        <v>1.44</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="R21" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="S21" t="n">
-        <v>3.18</v>
+        <v>1.97</v>
       </c>
       <c r="T21" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="U21" t="n">
-        <v>3.48</v>
+        <v>7.55</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="X21" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.199999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB21" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="AF21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>1.68</v>
       </c>
-      <c r="AG21" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AR21" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.76</v>
+        <v>1.18</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.28</v>
+        <v>5.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.42</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>6.28</v>
+        <v>3.3</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,28 +5135,28 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -5174,40 +5174,40 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5252,13 +5252,13 @@
         <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.16</v>
+        <v>1.42</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="R26" t="n">
-        <v>3.07</v>
+        <v>6.28</v>
       </c>
       <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2.63</v>
       </c>
-      <c r="T26" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF26" t="n">
+      <c r="AG26" t="n">
         <v>2.08</v>
       </c>
-      <c r="AG26" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AI26" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.53</v>
+        <v>2.75</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5646,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="R27" t="n">
-        <v>3.18</v>
+        <v>4.53</v>
       </c>
       <c r="S27" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="U27" t="n">
-        <v>4.4</v>
+        <v>5.06</v>
       </c>
       <c r="V27" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W27" t="n">
-        <v>2.85</v>
+        <v>2.48</v>
       </c>
       <c r="X27" t="n">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.65</v>
+        <v>7.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.23</v>
       </c>
-      <c r="AD27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AI27" t="n">
-        <v>5.25</v>
+        <v>6.9</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BB27" t="n">
         <v>1.25</v>
       </c>
-      <c r="AQ27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC27" t="n">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.17</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R28" t="n">
-        <v>2.24</v>
+        <v>3.18</v>
       </c>
       <c r="S28" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD28" t="n">
         <v>3.7</v>
       </c>
-      <c r="T28" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AE28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF28" t="n">
         <v>2.02</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AG28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK28" t="n">
         <v>1.65</v>
       </c>
-      <c r="AG28" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH28" t="n">
+      <c r="AL28" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BB28" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI28" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL28" t="n">
+      <c r="BC28" t="n">
         <v>1.85</v>
       </c>
-      <c r="AM28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="Q29" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BD29" t="n">
         <v>3.4</v>
       </c>
-      <c r="R29" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.86</v>
+        <v>2.57</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.6</v>
+        <v>2.65</v>
       </c>
       <c r="R30" t="n">
-        <v>3.77</v>
+        <v>2.91</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>3.13</v>
+        <v>2.34</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>2.34</v>
+        <v>3.07</v>
       </c>
       <c r="S32" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="T32" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="U32" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK32" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AL32" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.57</v>
+        <v>2.32</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="R33" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="S33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE34" t="n">
         <v>1.73</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R34" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U34" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BF34" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R35" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7383,52 +7383,52 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AU35" t="n">
         <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R37" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="S37" t="n">
         <v>2.21</v>
@@ -7720,10 +7720,10 @@
         <v>3.6</v>
       </c>
       <c r="X37" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Z37" t="n">
         <v>4.4</v>
@@ -7735,10 +7735,10 @@
         <v>1.01</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AD37" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AE37" t="n">
         <v>1.41</v>
@@ -7747,10 +7747,10 @@
         <v>2.52</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AI37" t="n">
         <v>3.34</v>
@@ -7765,7 +7765,7 @@
         <v>2.53</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AN37" t="n">
         <v>2.02</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="R38" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="S38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -7980,10 +7980,10 @@
         <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
         <v>0</v>
@@ -7995,31 +7995,31 @@
         <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>5.73</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.48</v>
+        <v>1.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="R39" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>12.01</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8177,10 +8177,10 @@
         <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AU39" t="n">
         <v>0</v>
@@ -8192,31 +8192,31 @@
         <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.32</v>
+        <v>3.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>6.09</v>
+        <v>3.84</v>
       </c>
       <c r="R41" t="n">
-        <v>10.6</v>
+        <v>2.06</v>
       </c>
       <c r="S41" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="X41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y41" t="n">
         <v>1.63</v>
       </c>
-      <c r="T41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U41" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W41" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.62</v>
-      </c>
       <c r="Z41" t="n">
-        <v>4.5</v>
+        <v>4.95</v>
       </c>
       <c r="AA41" t="n">
         <v>1.16</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC41" t="n">
         <v>1.14</v>
       </c>
       <c r="AD41" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AE41" t="n">
         <v>1.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AG41" t="n">
         <v>2.25</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AI41" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.9</v>
+        <v>1.44</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.85</v>
+        <v>2.66</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AN41" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.83</v>
+        <v>2.48</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.28</v>
+        <v>3.3</v>
       </c>
       <c r="AU41" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="AV41" t="n">
-        <v>3.05</v>
+        <v>2.23</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.32</v>
+        <v>1.76</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.85</v>
+        <v>1.46</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="BA41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BD41" t="n">
         <v>5.5</v>
       </c>
-      <c r="BB41" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>4.75</v>
-      </c>
       <c r="BE41" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.24</v>
+        <v>1.98</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.84</v>
+        <v>3.48</v>
       </c>
       <c r="R42" t="n">
-        <v>2.06</v>
+        <v>3.63</v>
       </c>
       <c r="S42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U42" t="n">
+        <v>4</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W42" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="X42" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU42" t="n">
         <v>3.35</v>
       </c>
-      <c r="T42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W42" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X42" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AV42" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AZ42" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="BD42" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="BE42" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.98</v>
+        <v>1.43</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.48</v>
+        <v>4.54</v>
       </c>
       <c r="R43" t="n">
-        <v>3.63</v>
+        <v>6.97</v>
       </c>
       <c r="S43" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="T43" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="U43" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="V43" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W43" t="n">
-        <v>2.81</v>
+        <v>3.15</v>
       </c>
       <c r="X43" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="Z43" t="n">
-        <v>6.85</v>
+        <v>6</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AE43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC43" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BD43" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.62</v>
+        <v>1.81</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.54</v>
+        <v>6.09</v>
       </c>
       <c r="R44" t="n">
-        <v>6.97</v>
+        <v>10.6</v>
       </c>
       <c r="S44" t="n">
-        <v>2.14</v>
+        <v>1.63</v>
       </c>
       <c r="T44" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="U44" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="V44" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W44" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="X44" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="Z44" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AD44" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="AI44" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BA44" t="n">
         <v>5.5</v>
       </c>
-      <c r="AJ44" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>3.15</v>
-      </c>
       <c r="BB44" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU45" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ45" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BA45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="R56" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11490,10 +11490,10 @@
         <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="R57" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -810,124 +810,124 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1461,7 +1461,7 @@
         <v>1.89</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AN5" t="n">
         <v>1.49</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R6" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>4.93</v>
+        <v>3.19</v>
       </c>
       <c r="T6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>1.7</v>
       </c>
-      <c r="U6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM6" t="n">
+      <c r="BA6" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.38</v>
       </c>
-      <c r="AN6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BF6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S7" t="n">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="W7" t="n">
-        <v>2.63</v>
+        <v>2.02</v>
       </c>
       <c r="X7" t="n">
-        <v>3.15</v>
+        <v>4.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AA7" t="n">
         <v>1.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.85</v>
+        <v>2.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.19</v>
+        <v>2.88</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AI7" t="n">
-        <v>8.1</v>
+        <v>13</v>
       </c>
       <c r="AJ7" t="n">
         <v>1.02</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.87</v>
+        <v>2.32</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1867,52 +1867,52 @@
         <v>1.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AT7" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>2.22</v>
+        <v>4.28</v>
       </c>
       <c r="T8" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="U8" t="n">
-        <v>5.04</v>
+        <v>2.87</v>
       </c>
       <c r="V8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX8" t="n">
         <v>1.32</v>
       </c>
-      <c r="W8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.89</v>
+        <v>2.34</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="S9" t="n">
-        <v>3.19</v>
+        <v>2.23</v>
       </c>
       <c r="T9" t="n">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
-        <v>3.95</v>
+        <v>4.89</v>
       </c>
       <c r="V9" t="n">
-        <v>1.59</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="X9" t="n">
-        <v>3.68</v>
+        <v>2.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.29</v>
+        <v>3.94</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.59</v>
+        <v>1.71</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.64</v>
+        <v>2.61</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.13</v>
+        <v>1.39</v>
       </c>
       <c r="AI9" t="n">
-        <v>12</v>
+        <v>4.75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.59</v>
+        <v>2.06</v>
       </c>
       <c r="AM9" t="n">
         <v>1.24</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.5</v>
+        <v>2.09</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.8</v>
+        <v>4.35</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2610,37 +2610,37 @@
         <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AM11" t="n">
         <v>1.33</v>
@@ -2691,7 +2691,7 @@
         <v>1.24</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="BD11" t="n">
         <v>3.3</v>
@@ -2700,7 +2700,7 @@
         <v>1.57</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3953,34 +3953,34 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.49</v>
+        <v>3.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="R18" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="X18" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z18" t="n">
         <v>7.2</v>
@@ -3989,40 +3989,40 @@
         <v>1.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AI18" t="n">
-        <v>6.55</v>
+        <v>7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AK18" t="n">
         <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.28</v>
+        <v>1.73</v>
       </c>
       <c r="AN18" t="n">
         <v>1.27</v>
@@ -4067,19 +4067,19 @@
         <v>1.62</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC18" t="n">
         <v>2.33</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="BE18" t="n">
         <v>1.62</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,16 +4544,16 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="R21" t="n">
-        <v>7.22</v>
+        <v>8</v>
       </c>
       <c r="S21" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="T21" t="n">
         <v>2.2</v>
@@ -4568,10 +4568,10 @@
         <v>2.69</v>
       </c>
       <c r="X21" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z21" t="n">
         <v>6.7</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,22 +4741,22 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4765,10 +4765,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -4780,40 +4780,40 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,13 +4858,13 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.05</v>
+        <v>1.42</v>
       </c>
       <c r="Q23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI23" t="n">
         <v>3.4</v>
       </c>
-      <c r="R23" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>5.96</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AL23" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,28 +5135,28 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -5174,40 +5174,40 @@
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5252,13 +5252,13 @@
         <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
         <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,28 +5332,28 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -5371,40 +5371,40 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5449,13 +5449,13 @@
         <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD25" t="n">
         <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>6.28</v>
+        <v>4.2</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>5.25</v>
+        <v>2.83</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.42</v>
+        <v>2.09</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.63</v>
+        <v>1.66</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.08</v>
+        <v>3.58</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.4</v>
+        <v>6.9</v>
       </c>
       <c r="AJ26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.26</v>
       </c>
-      <c r="AK26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AN26" t="n">
-        <v>2.75</v>
+        <v>1.78</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.73</v>
+        <v>2.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.34</v>
+        <v>3.46</v>
       </c>
       <c r="R27" t="n">
-        <v>4.53</v>
+        <v>2.37</v>
       </c>
       <c r="S27" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U27" t="n">
-        <v>5.06</v>
+        <v>2.95</v>
       </c>
       <c r="V27" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W27" t="n">
-        <v>2.48</v>
+        <v>3.08</v>
       </c>
       <c r="X27" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB27" t="n">
         <v>1.03</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.58</v>
+        <v>2.88</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AI27" t="n">
-        <v>6.9</v>
+        <v>5.45</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.91</v>
+        <v>1.62</v>
       </c>
       <c r="AL27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BE27" t="n">
         <v>1.8</v>
       </c>
-      <c r="AM27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.56</v>
-      </c>
       <c r="BF27" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>3.18</v>
+        <v>2.6</v>
       </c>
       <c r="S28" t="n">
-        <v>2.61</v>
+        <v>3.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="U28" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="V28" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W28" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="X28" t="n">
-        <v>2.65</v>
+        <v>3.08</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.65</v>
+        <v>7</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AD28" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="AG28" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.39</v>
+        <v>1.22</v>
       </c>
       <c r="AI28" t="n">
-        <v>5.25</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AL28" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AS28" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>2.2</v>
       </c>
-      <c r="AT28" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.68</v>
-      </c>
       <c r="BA28" t="n">
-        <v>2.48</v>
+        <v>1.86</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.88</v>
+        <v>2.32</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>2.27</v>
+        <v>2.9</v>
       </c>
       <c r="S29" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.57</v>
+        <v>2.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="S30" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="T30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS30" t="n">
         <v>1.85</v>
       </c>
-      <c r="U30" t="n">
+      <c r="AT30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD30" t="n">
         <v>3.7</v>
       </c>
-      <c r="V30" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>2.63</v>
-      </c>
       <c r="BE30" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="Q31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R31" t="n">
         <v>3.6</v>
       </c>
-      <c r="R31" t="n">
-        <v>2.34</v>
-      </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="T31" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U31" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="V31" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W31" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X31" t="n">
         <v>2.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AH31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR31" t="n">
         <v>1.42</v>
       </c>
-      <c r="AI31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AS31" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.35</v>
+        <v>2.05</v>
       </c>
       <c r="AU31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.74</v>
+        <v>2.6</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.45</v>
+        <v>2.04</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="Q32" t="n">
         <v>3.5</v>
       </c>
       <c r="R32" t="n">
-        <v>3.07</v>
+        <v>2.63</v>
       </c>
       <c r="S32" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="T32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW32" t="n">
         <v>2.33</v>
       </c>
-      <c r="U32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AM32" t="n">
+      <c r="AX32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB32" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
       <c r="BC32" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="R33" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,130 +7302,130 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R35" t="n">
         <v>3.6</v>
       </c>
       <c r="S35" t="n">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="T35" t="n">
         <v>2.3</v>
       </c>
       <c r="U35" t="n">
-        <v>3.8</v>
+        <v>4.35</v>
       </c>
       <c r="V35" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="W35" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="X35" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.6</v>
+        <v>6.65</v>
       </c>
       <c r="AA35" t="n">
         <v>1.08</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AE35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK35" t="n">
         <v>1.65</v>
       </c>
-      <c r="AF35" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AL35" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AV35" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>2.6</v>
+        <v>1.94</v>
       </c>
       <c r="AX35" t="n">
-        <v>2.04</v>
+        <v>1.58</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BC35" t="n">
         <v>1.85</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="BF35" t="n">
         <v>1.22</v>
@@ -7499,40 +7499,40 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="S36" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="T36" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="U36" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="V36" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W36" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="X36" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z36" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB36" t="n">
         <v>1.06</v>
@@ -7541,16 +7541,16 @@
         <v>1.3</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AH36" t="n">
         <v>1.25</v>
@@ -7562,16 +7562,16 @@
         <v>1.08</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -8287,61 +8287,61 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="R40" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="S40" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="T40" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="U40" t="n">
         <v>3.6</v>
       </c>
       <c r="V40" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W40" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="X40" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="Y40" t="n">
         <v>1.43</v>
       </c>
       <c r="Z40" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="AF40" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AI40" t="n">
         <v>5.3</v>
@@ -8410,10 +8410,10 @@
         <v>4</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.24</v>
+        <v>2.92</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="R41" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S41" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T41" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U41" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="V41" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W41" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="X41" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.95</v>
+        <v>5.2</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AD41" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AI41" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK41" t="n">
         <v>1.44</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="AM41" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF41" t="n">
         <v>1.29</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8681,16 +8681,16 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
         <v>3.63</v>
       </c>
       <c r="S42" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T42" t="n">
         <v>2.15</v>
@@ -8717,10 +8717,10 @@
         <v>1.04</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AD42" t="n">
         <v>3.3</v>
@@ -8732,16 +8732,16 @@
         <v>1.8</v>
       </c>
       <c r="AG42" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AI42" t="n">
-        <v>6.5</v>
+        <v>6.05</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AK42" t="n">
         <v>1.83</v>
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="R43" t="n">
-        <v>6.97</v>
+        <v>6.95</v>
       </c>
       <c r="S43" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="T43" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="U43" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="V43" t="n">
         <v>1.3</v>
       </c>
       <c r="W43" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="X43" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="Z43" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AD43" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG43" t="n">
-        <v>2.85</v>
+        <v>2.63</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AI43" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AN43" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8962,46 +8962,46 @@
         <v>1.23</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AU43" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AV43" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AX43" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="BA43" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="BF43" t="n">
         <v>1.22</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>6.09</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>10.6</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.09</v>
+        <v>3.25</v>
       </c>
       <c r="R55" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11293,10 +11293,10 @@
         <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R57" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11884,10 +11884,10 @@
         <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R60" t="n">
         <v>2.2</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -810,124 +810,124 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1007,124 +1007,124 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="S6" t="n">
-        <v>3.19</v>
+        <v>2.23</v>
       </c>
       <c r="T6" t="n">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
       <c r="U6" t="n">
-        <v>3.95</v>
+        <v>4.89</v>
       </c>
       <c r="V6" t="n">
-        <v>1.63</v>
+        <v>1.32</v>
       </c>
       <c r="W6" t="n">
-        <v>2.13</v>
+        <v>3.1</v>
       </c>
       <c r="X6" t="n">
-        <v>3.68</v>
+        <v>2.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="Z6" t="n">
-        <v>11</v>
+        <v>5.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.55</v>
+        <v>1.18</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.29</v>
+        <v>3.94</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.59</v>
+        <v>1.71</v>
       </c>
       <c r="AF6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AH6" t="n">
         <v>1.39</v>
       </c>
-      <c r="AG6" t="n">
-        <v>5.64</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AI6" t="n">
-        <v>12</v>
+        <v>4.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.61</v>
+        <v>2.06</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.48</v>
+        <v>2.09</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.7</v>
+        <v>1.91</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.74</v>
+        <v>4.35</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3.19</v>
       </c>
       <c r="T7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>1.7</v>
       </c>
-      <c r="U7" t="n">
-        <v>3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.7</v>
-      </c>
       <c r="BA7" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BC7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="S8" t="n">
-        <v>4.28</v>
+        <v>4.93</v>
       </c>
       <c r="T8" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="W8" t="n">
-        <v>2.63</v>
+        <v>2.02</v>
       </c>
       <c r="X8" t="n">
-        <v>3.22</v>
+        <v>4.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
         <v>1.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.83</v>
+        <v>2.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.19</v>
+        <v>3.07</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.65</v>
+        <v>1.32</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AI8" t="n">
-        <v>8.1</v>
+        <v>13</v>
       </c>
       <c r="AJ8" t="n">
         <v>1.02</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.87</v>
+        <v>2.32</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,52 +2064,52 @@
         <v>1.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.34</v>
+        <v>2.91</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>2.23</v>
+        <v>4.28</v>
       </c>
       <c r="T9" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="U9" t="n">
-        <v>4.89</v>
+        <v>2.87</v>
       </c>
       <c r="V9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX9" t="n">
         <v>1.32</v>
       </c>
-      <c r="W9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC9" t="n">
+      <c r="AY9" t="n">
         <v>1.18</v>
       </c>
-      <c r="AD9" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.35</v>
+        <v>3.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,22 +4741,22 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4765,10 +4765,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -4780,40 +4780,40 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,13 +4858,13 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>6.28</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4977,40 +4977,40 @@
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY24" t="n">
         <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.17</v>
+        <v>2.02</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="S25" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD25" t="n">
         <v>3.7</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AE25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF25" t="n">
         <v>2.02</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AG25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK25" t="n">
         <v>1.65</v>
       </c>
-      <c r="AG25" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH25" t="n">
+      <c r="AL25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BB25" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI25" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL25" t="n">
+      <c r="BC25" t="n">
         <v>1.85</v>
       </c>
-      <c r="AM25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.85</v>
+        <v>3.17</v>
       </c>
       <c r="Q26" t="n">
         <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>4.2</v>
+        <v>2.24</v>
       </c>
       <c r="S26" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U26" t="n">
-        <v>5.22</v>
+        <v>2.75</v>
       </c>
       <c r="V26" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W26" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="X26" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.09</v>
+        <v>2.02</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" t="n">
-        <v>6.9</v>
+        <v>6.75</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.04</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.91</v>
+        <v>2.16</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>2.37</v>
+        <v>3.07</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="T27" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="U27" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AI27" t="n">
-        <v>5.45</v>
+        <v>4.3</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
         <v>1.8</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AT30" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS30" t="n">
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC30" t="n">
         <v>1.85</v>
       </c>
-      <c r="AT30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.05</v>
-      </c>
       <c r="BD30" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,67 +6514,67 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="S31" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="T31" t="n">
         <v>2.3</v>
       </c>
       <c r="U31" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="V31" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="X31" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.66</v>
+        <v>5.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK31" t="n">
         <v>1.57</v>
@@ -6583,64 +6583,64 @@
         <v>2.25</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS31" t="n">
         <v>1.82</v>
       </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AT31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>2.05</v>
       </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AZ31" t="n">
+      <c r="BA31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE31" t="n">
         <v>1.73</v>
       </c>
-      <c r="BA31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BB31" t="n">
+      <c r="BF31" t="n">
         <v>1.2</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>2.63</v>
+        <v>4.06</v>
       </c>
       <c r="S32" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="U32" t="n">
-        <v>3.1</v>
+        <v>5.01</v>
       </c>
       <c r="V32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Y32" t="n">
         <v>1.33</v>
       </c>
-      <c r="W32" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z32" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BB32" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BC32" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.9</v>
+        <v>3.28</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="S33" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="T33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS33" t="n">
         <v>1.85</v>
       </c>
-      <c r="U33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y33" t="n">
+      <c r="AT33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF33" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.04</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>6.28</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7144,40 +7144,40 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.02</v>
+        <v>2.91</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="R35" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="S35" t="n">
-        <v>2.61</v>
+        <v>3.5</v>
       </c>
       <c r="T35" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="U35" t="n">
-        <v>4.35</v>
+        <v>2.95</v>
       </c>
       <c r="V35" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W35" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="X35" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z35" t="n">
-        <v>6.65</v>
+        <v>6.8</v>
       </c>
       <c r="AA35" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AK35" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL35" t="n">
         <v>2.15</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ35" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX35" t="n">
         <v>1.45</v>
       </c>
-      <c r="AR35" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AY35" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.48</v>
+        <v>1.06</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="R38" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>12.01</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -7980,10 +7980,10 @@
         <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AU38" t="n">
         <v>0</v>
@@ -7995,31 +7995,31 @@
         <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="Q39" t="n">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="R39" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="S39" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>12.01</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8177,10 +8177,10 @@
         <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AU39" t="n">
         <v>0</v>
@@ -8192,31 +8192,31 @@
         <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="R42" t="n">
-        <v>3.63</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S42" t="n">
-        <v>2.56</v>
+        <v>1.6</v>
       </c>
       <c r="T42" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="U42" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="V42" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="W42" t="n">
-        <v>2.81</v>
+        <v>3.84</v>
       </c>
       <c r="X42" t="n">
-        <v>2.81</v>
+        <v>2.21</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.38</v>
+        <v>1.69</v>
       </c>
       <c r="Z42" t="n">
-        <v>6.85</v>
+        <v>4.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AB42" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="AH42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AJ42" t="n">
         <v>1.27</v>
       </c>
-      <c r="AI42" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK42" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AM42" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ42" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN42" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AR42" t="n">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AS42" t="n">
-        <v>2.18</v>
+        <v>1.81</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.85</v>
+        <v>2.23</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.45</v>
+        <v>3.15</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="BA42" t="n">
-        <v>2.65</v>
+        <v>5.8</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.62</v>
+        <v>2.16</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS45" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AU45" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AX45" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BA45" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.24</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="R47" t="n">
-        <v>2.06</v>
+        <v>3.63</v>
       </c>
       <c r="S47" t="n">
-        <v>3.66</v>
+        <v>2.56</v>
       </c>
       <c r="T47" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="U47" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="V47" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="W47" t="n">
-        <v>3.66</v>
+        <v>2.81</v>
       </c>
       <c r="X47" t="n">
-        <v>2.2</v>
+        <v>2.81</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.95</v>
+        <v>6.85</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AD47" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.2</v>
+        <v>3.18</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.71</v>
+        <v>1.27</v>
       </c>
       <c r="AI47" t="n">
-        <v>3.8</v>
+        <v>6.05</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AL47" t="n">
-        <v>2.66</v>
+        <v>1.91</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="AT47" t="n">
-        <v>3.3</v>
+        <v>2.85</v>
       </c>
       <c r="AU47" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="AV47" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AZ47" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="BD47" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="BE47" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.09</v>
+        <v>3.07</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="R48" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="S48" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="T48" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="U48" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="V48" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="W48" t="n">
-        <v>2.41</v>
+        <v>3.5</v>
       </c>
       <c r="X48" t="n">
-        <v>3.4</v>
+        <v>2.19</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="Z48" t="n">
-        <v>11</v>
+        <v>4.33</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC48" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK48" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD48" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG48" t="n">
+      <c r="AL48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD48" t="n">
         <v>5</v>
       </c>
-      <c r="AH48" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BE48" t="n">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.1</v>
+        <v>1.39</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.07</v>
+        <v>2.09</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W49" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV49" t="n">
         <v>2</v>
       </c>
-      <c r="S49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U49" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL49" t="n">
+      <c r="AW49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA49" t="n">
         <v>2.7</v>
       </c>
-      <c r="AM49" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ49" t="n">
+      <c r="BB49" t="n">
         <v>1.4</v>
       </c>
-      <c r="AR49" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV49" t="n">
+      <c r="BC49" t="n">
         <v>2.7</v>
       </c>
-      <c r="AW49" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BD49" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="BE49" t="n">
-        <v>2.15</v>
+        <v>1.46</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.39</v>
+        <v>1.1</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,10 +11242,10 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R55" t="n">
         <v>2.2</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.09</v>
+        <v>3.6</v>
       </c>
       <c r="R58" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11884,10 +11884,10 @@
         <v>0</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12081,10 +12081,10 @@
         <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,10 +12227,10 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R60" t="n">
         <v>2.2</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G73" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.67</v>
+        <v>3.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="S6" t="n">
-        <v>2.23</v>
+        <v>4.28</v>
       </c>
       <c r="T6" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="U6" t="n">
-        <v>4.89</v>
+        <v>2.87</v>
       </c>
       <c r="V6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX6" t="n">
         <v>1.32</v>
       </c>
-      <c r="W6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AY6" t="n">
         <v>1.18</v>
       </c>
-      <c r="AD6" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.35</v>
+        <v>3.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W9" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="X9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF9" t="n">
         <v>2.1</v>
       </c>
-      <c r="S9" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG9" t="n">
-        <v>3.9</v>
+        <v>2.61</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="AI9" t="n">
-        <v>8.1</v>
+        <v>4.75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AL9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.83</v>
       </c>
-      <c r="AM9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2586,22 +2586,22 @@
         <v>2.63</v>
       </c>
       <c r="T11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U11" t="n">
         <v>3.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W11" t="n">
         <v>2.62</v>
       </c>
       <c r="X11" t="n">
-        <v>3.07</v>
+        <v>2.99</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
         <v>7.9</v>
@@ -2610,37 +2610,37 @@
         <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI11" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AM11" t="n">
         <v>1.33</v>
@@ -2691,16 +2691,16 @@
         <v>1.24</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="BE11" t="n">
         <v>1.57</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3953,10 +3953,10 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="R18" t="n">
         <v>2.05</v>
@@ -3968,7 +3968,7 @@
         <v>2.15</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="V18" t="n">
         <v>1.37</v>
@@ -3977,7 +3977,7 @@
         <v>2.69</v>
       </c>
       <c r="X18" t="n">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="Y18" t="n">
         <v>1.36</v>
@@ -4022,10 +4022,10 @@
         <v>1.95</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.73</v>
+        <v>1.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
         <v>1.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="BD18" t="n">
         <v>3.4</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.51</v>
+        <v>1.4</v>
       </c>
       <c r="Q20" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R20" t="n">
+        <v>8</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG20" t="n">
         <v>3.2</v>
       </c>
-      <c r="R20" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="V20" t="n">
+      <c r="AH20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
         <v>1.4</v>
       </c>
-      <c r="W20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.76</v>
+        <v>1.18</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.28</v>
+        <v>5.1</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Panathinaikos</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>7.55</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,28 +4741,28 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -4780,40 +4780,40 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,13 +4858,13 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV24" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U24" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y24" t="n">
+      <c r="AW24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.04</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.02</v>
+        <v>2.91</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="R25" t="n">
-        <v>3.6</v>
+        <v>2.37</v>
       </c>
       <c r="S25" t="n">
-        <v>2.61</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="U25" t="n">
-        <v>4.35</v>
+        <v>2.95</v>
       </c>
       <c r="V25" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W25" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="X25" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.65</v>
+        <v>6.8</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AK25" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL25" t="n">
         <v>2.15</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AQ25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX25" t="n">
         <v>1.45</v>
       </c>
-      <c r="AR25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AY25" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.17</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="R26" t="n">
-        <v>2.24</v>
+        <v>3.07</v>
       </c>
       <c r="S26" t="n">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="T26" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2.08</v>
       </c>
-      <c r="U26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AG26" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI26" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AN26" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5646,13 +5646,13 @@
         <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="BD26" t="n">
         <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="BF26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,22 +5726,22 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -5750,10 +5750,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -5765,40 +5765,40 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5843,13 +5843,13 @@
         <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
         <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R28" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R28" t="n">
-        <v>2.6</v>
-      </c>
       <c r="S28" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="T28" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="U28" t="n">
-        <v>2.9</v>
+        <v>4.28</v>
       </c>
       <c r="V28" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM28" t="n">
         <v>1.4</v>
       </c>
-      <c r="W28" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ28" t="n">
+      <c r="AN28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BF28" t="n">
         <v>1.04</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R29" t="n">
         <v>3.3</v>
       </c>
-      <c r="R29" t="n">
-        <v>2.9</v>
-      </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="S30" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="T30" t="n">
         <v>2.3</v>
       </c>
       <c r="U30" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="V30" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W30" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV30" t="n">
         <v>3.1</v>
       </c>
-      <c r="X30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC30" t="n">
+      <c r="AW30" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BF30" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,67 +6514,67 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R31" t="n">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="S31" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="T31" t="n">
         <v>2.3</v>
       </c>
       <c r="U31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W31" t="n">
         <v>3.1</v>
       </c>
-      <c r="V31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.99</v>
-      </c>
       <c r="X31" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="Y31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.44</v>
       </c>
-      <c r="Z31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AI31" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK31" t="n">
         <v>1.57</v>
@@ -6583,64 +6583,64 @@
         <v>2.25</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AU31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.86</v>
+        <v>2.04</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AZ31" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="BB31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF31" t="n">
         <v>1.22</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>4.06</v>
+        <v>2.9</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>3.3</v>
+        <v>4.06</v>
       </c>
       <c r="S33" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U33" t="n">
-        <v>3.75</v>
+        <v>5.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="W33" t="n">
-        <v>2.77</v>
+        <v>2.48</v>
       </c>
       <c r="X33" t="n">
-        <v>2.73</v>
+        <v>3.21</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.34</v>
+        <v>2.83</v>
       </c>
       <c r="AE33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW33" t="n">
         <v>1.87</v>
       </c>
-      <c r="AF33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="AJ33" t="n">
+      <c r="AX33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BF33" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.42</v>
+        <v>2.52</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>6.28</v>
+        <v>2.6</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AD34" t="n">
-        <v>5.25</v>
+        <v>2.9</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.42</v>
+        <v>2.15</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.08</v>
+        <v>3.9</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AI34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BD34" t="n">
         <v>3.4</v>
       </c>
-      <c r="AJ34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AM34" t="n">
+      <c r="BE34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BF34" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.91</v>
+        <v>1.42</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.46</v>
+        <v>4.6</v>
       </c>
       <c r="R35" t="n">
-        <v>2.37</v>
+        <v>6.28</v>
       </c>
       <c r="S35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>1.26</v>
       </c>
-      <c r="AD35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK35" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.62</v>
+        <v>1.14</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.44</v>
+        <v>2.75</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7499,34 +7499,34 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R36" t="n">
         <v>3.3</v>
       </c>
-      <c r="R36" t="n">
-        <v>3.4</v>
-      </c>
       <c r="S36" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="T36" t="n">
         <v>2.15</v>
       </c>
       <c r="U36" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="V36" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W36" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="X36" t="n">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z36" t="n">
         <v>7.1</v>
@@ -7550,7 +7550,7 @@
         <v>1.75</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="AH36" t="n">
         <v>1.25</v>
@@ -7571,7 +7571,7 @@
         <v>1.33</v>
       </c>
       <c r="AN36" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
@@ -7613,16 +7613,16 @@
         <v>2.18</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BC36" t="n">
         <v>2.2</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF36" t="n">
         <v>1.15</v>
@@ -7911,10 +7911,10 @@
         <v>12.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W38" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="X38" t="n">
         <v>1.86</v>
@@ -7926,19 +7926,19 @@
         <v>3.7</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AB38" t="n">
         <v>1.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AD38" t="n">
         <v>7.6</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF38" t="n">
         <v>3.2</v>
@@ -8287,28 +8287,28 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="S40" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="T40" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="U40" t="n">
         <v>3.6</v>
       </c>
       <c r="V40" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W40" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="X40" t="n">
         <v>2.59</v>
@@ -8317,13 +8317,13 @@
         <v>1.43</v>
       </c>
       <c r="Z40" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AC40" t="n">
         <v>1.2</v>
@@ -8332,22 +8332,22 @@
         <v>3.68</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AI40" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AK40" t="n">
         <v>1.62</v>
@@ -8404,13 +8404,13 @@
         <v>1.22</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="BD40" t="n">
         <v>4</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="BF40" t="n">
         <v>1.18</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="Q42" t="n">
-        <v>6</v>
+        <v>5.05</v>
       </c>
       <c r="R42" t="n">
-        <v>9.949999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="S42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8878,31 +8878,31 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="R43" t="n">
-        <v>6.95</v>
+        <v>6.74</v>
       </c>
       <c r="S43" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="T43" t="n">
         <v>2.45</v>
       </c>
       <c r="U43" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="V43" t="n">
         <v>1.3</v>
       </c>
       <c r="W43" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="X43" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="Y43" t="n">
         <v>1.49</v>
@@ -8923,10 +8923,10 @@
         <v>4.2</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG43" t="n">
         <v>2.63</v>
@@ -8935,7 +8935,7 @@
         <v>1.4</v>
       </c>
       <c r="AI43" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AJ43" t="n">
         <v>1.17</v>
@@ -8944,7 +8944,7 @@
         <v>1.8</v>
       </c>
       <c r="AL43" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AM43" t="n">
         <v>1.2</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,130 +9075,130 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.24</v>
+        <v>1.2</v>
       </c>
       <c r="Q44" t="n">
+        <v>7</v>
+      </c>
+      <c r="R44" t="n">
+        <v>13</v>
+      </c>
+      <c r="S44" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U44" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W44" t="n">
         <v>3.84</v>
       </c>
-      <c r="R44" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U44" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W44" t="n">
-        <v>3.66</v>
-      </c>
       <c r="X44" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.95</v>
+        <v>4.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AB44" t="n">
         <v>1.02</v>
       </c>
       <c r="AC44" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AZ44" t="n">
         <v>1.14</v>
       </c>
-      <c r="AD44" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH44" t="n">
+      <c r="BA44" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC44" t="n">
         <v>1.71</v>
       </c>
-      <c r="AI44" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>1.73</v>
-      </c>
       <c r="BD44" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BE44" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BF44" t="n">
         <v>1.3</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Motherwell</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Motherwell</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,133 +9666,133 @@
         </is>
       </c>
       <c r="P47" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W47" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X47" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE47" t="n">
         <v>2</v>
       </c>
-      <c r="Q47" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R47" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T47" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U47" t="n">
-        <v>4</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W47" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="X47" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP47" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX47" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ47" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB47" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BF47" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.07</v>
+        <v>2.08</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.45</v>
+        <v>3.24</v>
       </c>
       <c r="R48" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S48" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W48" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="X48" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV48" t="n">
         <v>2</v>
       </c>
-      <c r="S48" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T48" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U48" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W48" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X48" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK48" t="n">
+      <c r="AW48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE48" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BF48" t="n">
-        <v>1.39</v>
+        <v>1.1</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.09</v>
+        <v>3.05</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="R49" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="S49" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="T49" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="U49" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="V49" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="W49" t="n">
-        <v>2.41</v>
+        <v>3.5</v>
       </c>
       <c r="X49" t="n">
-        <v>3.4</v>
+        <v>2.19</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="Z49" t="n">
-        <v>11</v>
+        <v>4.33</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC49" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK49" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD49" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG49" t="n">
+      <c r="AL49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD49" t="n">
         <v>5</v>
       </c>
-      <c r="AH49" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BE49" t="n">
-        <v>1.46</v>
+        <v>2.15</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,10 +11242,10 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R55" t="n">
         <v>2.2</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.85</v>
+        <v>3.1</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="R58" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.09</v>
+        <v>3.2</v>
       </c>
       <c r="R59" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12081,10 +12081,10 @@
         <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.25</v>
+        <v>4.09</v>
       </c>
       <c r="R60" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12278,10 +12278,10 @@
         <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.3</v>
+        <v>3.96</v>
       </c>
       <c r="R69" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G73" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,43 +998,43 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="S3" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
-        <v>4.62</v>
+        <v>3.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W3" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="X3" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC3" t="n">
         <v>1.3</v>
@@ -1043,88 +1043,88 @@
         <v>3.1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AH3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1.28</v>
       </c>
-      <c r="AI3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.1</v>
+        <v>2.02</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BE3" t="n">
         <v>1.62</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
+        <v>3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W6" t="n">
         <v>2.1</v>
       </c>
-      <c r="S6" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.63</v>
-      </c>
       <c r="X6" t="n">
-        <v>3.22</v>
+        <v>3.68</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.83</v>
+        <v>2.29</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.19</v>
+        <v>2.59</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.9</v>
+        <v>5.64</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AI6" t="n">
-        <v>8.1</v>
+        <v>12</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AV6" t="n">
         <v>1.87</v>
       </c>
-      <c r="AL6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AW6" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AX6" t="n">
         <v>1.32</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.43</v>
+        <v>1.7</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.64</v>
+        <v>2.35</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>3.82</v>
       </c>
       <c r="R7" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3.19</v>
+        <v>2.24</v>
       </c>
       <c r="T7" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="U7" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.59</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF7" t="n">
         <v>2.1</v>
       </c>
-      <c r="X7" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AG7" t="n">
-        <v>5.64</v>
+        <v>2.63</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" t="n">
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.61</v>
+        <v>2.11</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>4.93</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="W8" t="n">
-        <v>2.02</v>
+        <v>2.65</v>
       </c>
       <c r="X8" t="n">
-        <v>4.05</v>
+        <v>2.96</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="Z8" t="n">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.23</v>
+        <v>3.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.07</v>
+        <v>2.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
-        <v>5.8</v>
+        <v>3.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AI8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,52 +2064,52 @@
         <v>1.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AW8" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA8" t="n">
         <v>1.64</v>
       </c>
-      <c r="AX8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BB8" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.91</v>
+        <v>2.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.59</v>
+        <v>3.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="R9" t="n">
-        <v>4.5</v>
+        <v>2.27</v>
       </c>
       <c r="S9" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD9" t="n">
         <v>2.23</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U9" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="AE9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.32</v>
       </c>
-      <c r="W9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="AG9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="AI9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR9" t="n">
         <v>2.1</v>
       </c>
-      <c r="AG9" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.91</v>
+        <v>2.91</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.35</v>
+        <v>2.59</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2580,7 +2580,7 @@
         <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="S11" t="n">
         <v>2.63</v>
@@ -2592,16 +2592,16 @@
         <v>3.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
         <v>2.62</v>
       </c>
       <c r="X11" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
         <v>7.9</v>
@@ -2610,31 +2610,31 @@
         <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI11" t="n">
         <v>7</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
         <v>1.83</v>
@@ -2694,13 +2694,13 @@
         <v>2.25</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="BE11" t="n">
         <v>1.57</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>11.8</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S18" t="n">
         <v>3.9</v>
@@ -3974,7 +3974,7 @@
         <v>1.37</v>
       </c>
       <c r="W18" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="X18" t="n">
         <v>2.91</v>
@@ -4067,16 +4067,16 @@
         <v>1.62</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC18" t="n">
         <v>2.17</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BF18" t="n">
         <v>1.15</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4347,16 +4347,16 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="R20" t="n">
         <v>8</v>
       </c>
       <c r="S20" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="T20" t="n">
         <v>2.2</v>
@@ -4371,7 +4371,7 @@
         <v>2.69</v>
       </c>
       <c r="X20" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="Y20" t="n">
         <v>1.4</v>
@@ -4392,7 +4392,7 @@
         <v>3.12</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AF20" t="n">
         <v>1.8</v>
@@ -4401,13 +4401,13 @@
         <v>3.2</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AI20" t="n">
         <v>6.05</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AK20" t="n">
         <v>2.18</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY21" t="n">
         <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,28 +4741,28 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -4780,40 +4780,40 @@
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,13 +4858,13 @@
         <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>3.17</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="S24" t="n">
-        <v>2.67</v>
+        <v>3.7</v>
       </c>
       <c r="T24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
         <v>2.2</v>
       </c>
-      <c r="U24" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.05</v>
-      </c>
       <c r="BD24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.82</v>
+        <v>1.52</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R26" t="n">
-        <v>3.07</v>
+        <v>3.6</v>
       </c>
       <c r="S26" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X26" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AD26" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.08</v>
+        <v>2.17</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AI26" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.15</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AM26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BF26" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.58</v>
+        <v>2.64</v>
       </c>
       <c r="T28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.85</v>
       </c>
-      <c r="U28" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y28" t="n">
+      <c r="AF28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AQ28" t="n">
-        <v>1.81</v>
+        <v>1.32</v>
       </c>
       <c r="AR28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AT28" t="n">
         <v>2.3</v>
       </c>
-      <c r="AS28" t="n">
+      <c r="AU28" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AV28" t="n">
         <v>3.05</v>
       </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AW28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AY28" t="n">
         <v>1.53</v>
       </c>
-      <c r="AX28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ28" t="n">
-        <v>1.97</v>
+        <v>1.72</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="BC28" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="BD28" t="n">
-        <v>2.62</v>
+        <v>3.88</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>2.91</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="R29" t="n">
-        <v>3.3</v>
+        <v>2.37</v>
       </c>
       <c r="S29" t="n">
-        <v>2.64</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W29" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV29" t="n">
         <v>2.2</v>
       </c>
-      <c r="U29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>5.96</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AW29" t="n">
-        <v>2.3</v>
+        <v>1.74</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BC29" t="n">
         <v>2.05</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="Q30" t="n">
         <v>3.5</v>
       </c>
       <c r="R30" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="S30" t="n">
         <v>2.63</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T30" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL30" t="n">
         <v>2.3</v>
       </c>
-      <c r="U30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC30" t="n">
+      <c r="AM30" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AN30" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.9</v>
+        <v>1.42</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="R31" t="n">
-        <v>3.6</v>
+        <v>6.28</v>
       </c>
       <c r="S31" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="T31" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="U31" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W31" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="X31" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.6</v>
+        <v>5.12</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AB31" t="n">
         <v>1.03</v>
       </c>
       <c r="AC31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.17</v>
       </c>
       <c r="AK31" t="n">
         <v>1.57</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6595,52 +6595,52 @@
         <v>0</v>
       </c>
       <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BF31" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AT32" t="n">
         <v>2.9</v>
       </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.85</v>
+        <v>2.52</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>4.06</v>
+        <v>2.6</v>
       </c>
       <c r="S33" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="T33" t="n">
         <v>2.1</v>
       </c>
       <c r="U33" t="n">
-        <v>5.01</v>
+        <v>2.9</v>
       </c>
       <c r="V33" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W33" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="X33" t="n">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="Z33" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AI33" t="n">
-        <v>6.9</v>
+        <v>8</v>
       </c>
       <c r="AJ33" t="n">
         <v>1.04</v>
       </c>
       <c r="AK33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BA33" t="n">
         <v>1.89</v>
       </c>
-      <c r="AL33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
+      <c r="BB33" t="n">
         <v>1.29</v>
       </c>
-      <c r="AQ33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC33" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.52</v>
+        <v>2.05</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="R34" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="S34" t="n">
-        <v>3.3</v>
+        <v>2.67</v>
       </c>
       <c r="T34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL34" t="n">
         <v>2.1</v>
       </c>
-      <c r="U34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W34" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X34" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AM34" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="R35" t="n">
-        <v>6.28</v>
+        <v>2.8</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.12</v>
+        <v>1.61</v>
       </c>
       <c r="AD35" t="n">
-        <v>5.25</v>
+        <v>2.17</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.42</v>
+        <v>2.78</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.63</v>
+        <v>1.34</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.08</v>
+        <v>5.4</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.65</v>
+        <v>1.09</v>
       </c>
       <c r="AI35" t="n">
-        <v>3.4</v>
+        <v>13.5</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.75</v>
+        <v>1.39</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY35" t="n">
         <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7499,28 +7499,28 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R36" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="S36" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T36" t="n">
         <v>2.15</v>
       </c>
       <c r="U36" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="V36" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W36" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="X36" t="n">
         <v>2.85</v>
@@ -7535,31 +7535,31 @@
         <v>1.04</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AI36" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AK36" t="n">
         <v>1.75</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,79 +7893,79 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="R38" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="S38" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>12.01</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
@@ -7980,10 +7980,10 @@
         <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
         <v>0</v>
@@ -7995,31 +7995,31 @@
         <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,79 +8090,79 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.48</v>
+        <v>1.06</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="R39" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>12.01</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
@@ -8177,10 +8177,10 @@
         <v>0</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AU39" t="n">
         <v>0</v>
@@ -8192,31 +8192,31 @@
         <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8290,10 +8290,10 @@
         <v>2.06</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R40" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="S40" t="n">
         <v>2.5</v>
@@ -8317,7 +8317,7 @@
         <v>1.43</v>
       </c>
       <c r="Z40" t="n">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="AA40" t="n">
         <v>1.06</v>
@@ -8326,7 +8326,7 @@
         <v>1.04</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AD40" t="n">
         <v>3.68</v>
@@ -8335,16 +8335,16 @@
         <v>1.75</v>
       </c>
       <c r="AF40" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AH40" t="n">
         <v>1.36</v>
       </c>
       <c r="AI40" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ40" t="n">
         <v>1.13</v>
@@ -8404,13 +8404,13 @@
         <v>1.22</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="BD40" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="BF40" t="n">
         <v>1.18</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.24</v>
+        <v>1.34</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.84</v>
+        <v>5.05</v>
       </c>
       <c r="R41" t="n">
-        <v>2.06</v>
+        <v>7.78</v>
       </c>
       <c r="S41" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.05</v>
+        <v>4.55</v>
       </c>
       <c r="R42" t="n">
-        <v>7.78</v>
+        <v>6.74</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>7</v>
+      </c>
+      <c r="R43" t="n">
+        <v>13</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U43" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W43" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE43" t="n">
         <v>1.43</v>
       </c>
-      <c r="Q43" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="R43" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="S43" t="n">
+      <c r="AF43" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK43" t="n">
         <v>1.9</v>
       </c>
-      <c r="T43" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U43" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="V43" t="n">
+      <c r="AL43" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF43" t="n">
         <v>1.3</v>
-      </c>
-      <c r="W43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>1.22</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Club Always Ready</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
-        <v>3.63</v>
+        <v>4.13</v>
       </c>
       <c r="S45" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T45" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="U45" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="V45" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W45" t="n">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="X45" t="n">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z45" t="n">
-        <v>6.85</v>
+        <v>7.8</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB45" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AD45" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AE45" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK45" t="n">
         <v>1.91</v>
       </c>
-      <c r="AF45" t="n">
+      <c r="AL45" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>1.91</v>
       </c>
       <c r="AM45" t="n">
         <v>1.3</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>2.65</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="BD45" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Always Ready</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,133 +9863,133 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.08</v>
+        <v>3.05</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.24</v>
+        <v>3.8</v>
       </c>
       <c r="R48" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="S48" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="T48" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="U48" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="V48" t="n">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="W48" t="n">
-        <v>2.41</v>
+        <v>3.5</v>
       </c>
       <c r="X48" t="n">
-        <v>3.66</v>
+        <v>2.19</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.26</v>
+        <v>1.7</v>
       </c>
       <c r="Z48" t="n">
-        <v>11</v>
+        <v>4.33</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC48" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK48" t="n">
         <v>1.44</v>
       </c>
-      <c r="AD48" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG48" t="n">
+      <c r="AL48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD48" t="n">
         <v>5</v>
       </c>
-      <c r="AH48" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BE48" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,133 +10060,133 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q49" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R49" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S49" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W49" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="X49" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AT49" t="n">
         <v>3.8</v>
       </c>
-      <c r="R49" t="n">
+      <c r="AU49" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV49" t="n">
         <v>2</v>
       </c>
-      <c r="S49" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U49" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W49" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AH49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK49" t="n">
+      <c r="AW49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE49" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE49" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BF49" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Independiente Petrolero</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Independiente Petrolero</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Jose Earthquakes II</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>San Jose Earthquakes II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,10 +11833,10 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="R58" t="n">
         <v>2.2</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,10 +12030,10 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R59" t="n">
         <v>2.2</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>FC Cincinnati II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FC Cincinnati II</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>St. Louis City</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>St. Louis City</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G73" t="n">

--- a/jogos_2026-05-13.xlsx
+++ b/jogos_2026-05-13.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bucheon 1995</t>
+          <t>Ulsan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>Jeju United</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ulsan</t>
+          <t>Bucheon 1995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jeju United</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>3.82</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.19</v>
+        <v>2.24</v>
       </c>
       <c r="T6" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.59</v>
+        <v>1.31</v>
       </c>
       <c r="W6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AF6" t="n">
         <v>2.1</v>
       </c>
-      <c r="X6" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.39</v>
-      </c>
       <c r="AG6" t="n">
-        <v>5.64</v>
+        <v>2.63</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
-        <v>12</v>
+        <v>4.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.15</v>
+        <v>1.63</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.61</v>
+        <v>2.11</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.74</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL7" t="n">
         <v>1.61</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="R7" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AM7" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.91</v>
+        <v>2.7</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>2.74</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>4.93</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="W8" t="n">
-        <v>2.65</v>
+        <v>2.02</v>
       </c>
       <c r="X8" t="n">
-        <v>2.96</v>
+        <v>4.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.5</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.2</v>
+        <v>2.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.01</v>
+        <v>2.88</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.38</v>
+        <v>5.85</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AI8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2064,52 +2064,52 @@
         <v>1.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.2</v>
+        <v>2.91</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>4.93</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>2.02</v>
+        <v>2.65</v>
       </c>
       <c r="X9" t="n">
-        <v>4.05</v>
+        <v>2.96</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.16</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.63</v>
+        <v>1.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.23</v>
+        <v>3.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>3.07</v>
+        <v>2.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.8</v>
+        <v>3.38</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2261,52 +2261,52 @@
         <v>1.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AW9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BA9" t="n">
         <v>1.64</v>
       </c>
-      <c r="AX9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BB9" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.91</v>
+        <v>2.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.59</v>
+        <v>3.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>AEK Athens</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AEK Athens</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG21"